--- a/static/exercises/brain/brain exercise.xlsx
+++ b/static/exercises/brain/brain exercise.xlsx
@@ -1,25 +1,221 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prazzol\sajhya.com\static\exercises\brain\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE73C2D-BBE4-4206-9B71-EEF8C0C761F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="58">
+  <si>
+    <t>/static/exercises/brain/arm positioning.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/affected side down.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/affected side up.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Ankle Dorsiflexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Ankle Eversion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Ankle Plantar Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Diaphramatic Breathing.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/heel slide.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/limb positioning.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Ankle Plantar Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Elbow Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Hip Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Knee Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Shoulder Extension.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Shoulder Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Wrist Extension.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/Passive Wrist Flexion.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/quad isometric.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/supine pelvic tilt.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/seated pelvic tilt.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/seated scapular retraction.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/seated trunk rotation.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/seated weight shift antpost.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/seated weight shift lateral.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/supine arm slides.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/supine positioning.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/table top arm slide.png</t>
+  </si>
+  <si>
+    <t>/static/exercises/brain/towel squeeze.png</t>
+  </si>
+  <si>
+    <t>Passive Shoulder Flexion (Supine - Affected side)</t>
+  </si>
+  <si>
+    <t>Passive Shoulder External Rotation (Supine)</t>
+  </si>
+  <si>
+    <t>Passive Elbow Flexion/Extension (Affected side)</t>
+  </si>
+  <si>
+    <t>Passive Forearm Pronation/Supination</t>
+  </si>
+  <si>
+    <t>Passive Wrist Flexion/Extension (Affected side)</t>
+  </si>
+  <si>
+    <t>Passive Finger Flexion/Extension</t>
+  </si>
+  <si>
+    <t>Passive Thumb Abduction/Adduction</t>
+  </si>
+  <si>
+    <t>Passive Hip Flexion (Supine - Affected side)</t>
+  </si>
+  <si>
+    <t>Passive Hip Abduction/Adduction (Supine)</t>
+  </si>
+  <si>
+    <t>Passive Knee Flexion/Extension (Supine)</t>
+  </si>
+  <si>
+    <t>Passive Ankle Dorsiflexion/Plantarflexion</t>
+  </si>
+  <si>
+    <t>Passive Ankle Inversion/Eversion</t>
+  </si>
+  <si>
+    <t>Affected Limb Positioning (Pillow support)</t>
+  </si>
+  <si>
+    <t>Sidelying Positioning (Affected side up)</t>
+  </si>
+  <si>
+    <t>Sidelying Positioning (Affected side down)</t>
+  </si>
+  <si>
+    <t>Supine Positioning (Neutral alignment)</t>
+  </si>
+  <si>
+    <t>Deep Breathing (Diaphragmatic)</t>
+  </si>
+  <si>
+    <t>Seated Supported Scapular Retraction</t>
+  </si>
+  <si>
+    <t>Table Top Arm Slides (Affected side)</t>
+  </si>
+  <si>
+    <t>Supine Arm Slides (Affected side)</t>
+  </si>
+  <si>
+    <t>Supine Heel Slides (Affected side)</t>
+  </si>
+  <si>
+    <t>Seated Weight Shifts (Lateral)</t>
+  </si>
+  <si>
+    <t>Seated Weight Shifts (Anterior/Posterior)</t>
+  </si>
+  <si>
+    <t>Seated Trunk Rotation (Arms crossed)</t>
+  </si>
+  <si>
+    <t>Seated Pelvic Tilt</t>
+  </si>
+  <si>
+    <t>Isometric Quadriceps Set (Affected side)</t>
+  </si>
+  <si>
+    <t>Isometric Glute Set (Affected side)</t>
+  </si>
+  <si>
+    <t>Towel Squeeze (Affected hand - Assisted)</t>
+  </si>
+  <si>
+    <t>WHEN</t>
+  </si>
+  <si>
+    <t>THEN</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,8 +245,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +527,870 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D1" s="1"/>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1">
+        <v>2595</v>
+      </c>
+      <c r="P1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q1">
+        <f>M1</f>
+        <v>2595</v>
+      </c>
+      <c r="R1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S1" t="str">
+        <f>G1</f>
+        <v>/static/exercises/brain/Passive Shoulder Flexion.png</v>
+      </c>
+      <c r="Y1" t="str">
+        <f>""&amp;P1&amp;" "&amp;Q1&amp;" "&amp;R1&amp;" '"&amp;S1&amp;"'"</f>
+        <v>WHEN 2595 THEN '/static/exercises/brain/Passive Shoulder Flexion.png'</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D2" s="1"/>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2">
+        <f>M1+1</f>
+        <v>2596</v>
+      </c>
+      <c r="P2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:Q28" si="0">M2</f>
+        <v>2596</v>
+      </c>
+      <c r="R2" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" t="str">
+        <f t="shared" ref="S2:S28" si="1">G2</f>
+        <v>/static/exercises/brain/affected side up.png</v>
+      </c>
+      <c r="Y2" t="str">
+        <f t="shared" ref="Y2:Y28" si="2">""&amp;P2&amp;" "&amp;Q2&amp;" "&amp;R2&amp;" '"&amp;S2&amp;"'"</f>
+        <v>WHEN 2596 THEN '/static/exercises/brain/affected side up.png'</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D3" s="1"/>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M28" si="3">M2+1</f>
+        <v>2597</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>2597</v>
+      </c>
+      <c r="R3" t="s">
+        <v>57</v>
+      </c>
+      <c r="S3" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Shoulder Extension.png</v>
+      </c>
+      <c r="Y3" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2597 THEN '/static/exercises/brain/Passive Shoulder Extension.png'</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="3"/>
+        <v>2598</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>2598</v>
+      </c>
+      <c r="R4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S4" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Wrist Flexion.png</v>
+      </c>
+      <c r="Y4" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2598 THEN '/static/exercises/brain/Passive Wrist Flexion.png'</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D5" s="1"/>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="3"/>
+        <v>2599</v>
+      </c>
+      <c r="P5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>2599</v>
+      </c>
+      <c r="R5" t="s">
+        <v>57</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Wrist Extension.png</v>
+      </c>
+      <c r="Y5" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2599 THEN '/static/exercises/brain/Passive Wrist Extension.png'</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="3"/>
+        <v>2600</v>
+      </c>
+      <c r="P6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>2600</v>
+      </c>
+      <c r="R6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Elbow Flexion.png</v>
+      </c>
+      <c r="Y6" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2600 THEN '/static/exercises/brain/Passive Elbow Flexion.png'</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D7" s="1"/>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="3"/>
+        <v>2601</v>
+      </c>
+      <c r="P7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>2601</v>
+      </c>
+      <c r="R7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2601 THEN ''</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D8" s="1"/>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="3"/>
+        <v>2602</v>
+      </c>
+      <c r="P8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>2602</v>
+      </c>
+      <c r="R8" t="s">
+        <v>57</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Hip Flexion.png</v>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2602 THEN '/static/exercises/brain/Passive Hip Flexion.png'</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D9" s="1"/>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="3"/>
+        <v>2603</v>
+      </c>
+      <c r="P9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>2603</v>
+      </c>
+      <c r="R9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2603 THEN ''</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D10" s="1"/>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="3"/>
+        <v>2604</v>
+      </c>
+      <c r="P10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>2604</v>
+      </c>
+      <c r="R10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Knee Flexion.png</v>
+      </c>
+      <c r="Y10" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2604 THEN '/static/exercises/brain/Passive Knee Flexion.png'</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D11" s="1"/>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>2605</v>
+      </c>
+      <c r="P11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>2605</v>
+      </c>
+      <c r="R11" t="s">
+        <v>57</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Passive Ankle Plantar Flexion.png</v>
+      </c>
+      <c r="Y11" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2605 THEN '/static/exercises/brain/Passive Ankle Plantar Flexion.png'</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D12" s="1"/>
+      <c r="G12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="3"/>
+        <v>2606</v>
+      </c>
+      <c r="P12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>2606</v>
+      </c>
+      <c r="R12" t="s">
+        <v>57</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Ankle Eversion.png</v>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2606 THEN '/static/exercises/brain/Ankle Eversion.png'</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D13" s="1"/>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
+        <v>2607</v>
+      </c>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>2607</v>
+      </c>
+      <c r="R13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/limb positioning.png</v>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2607 THEN '/static/exercises/brain/limb positioning.png'</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D14" s="1"/>
+      <c r="G14" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="3"/>
+        <v>2608</v>
+      </c>
+      <c r="P14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>2608</v>
+      </c>
+      <c r="R14" t="s">
+        <v>57</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/arm positioning.png</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2608 THEN '/static/exercises/brain/arm positioning.png'</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D15" s="1"/>
+      <c r="G15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>2609</v>
+      </c>
+      <c r="P15" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>2609</v>
+      </c>
+      <c r="R15" t="s">
+        <v>57</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/affected side down.png</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2609 THEN '/static/exercises/brain/affected side down.png'</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D16" s="1"/>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="3"/>
+        <v>2610</v>
+      </c>
+      <c r="P16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>2610</v>
+      </c>
+      <c r="R16" t="s">
+        <v>57</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/supine positioning.png</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2610 THEN '/static/exercises/brain/supine positioning.png'</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D17" s="1"/>
+      <c r="G17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>2611</v>
+      </c>
+      <c r="P17" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>2611</v>
+      </c>
+      <c r="R17" t="s">
+        <v>57</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/Diaphramatic Breathing.png</v>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2611 THEN '/static/exercises/brain/Diaphramatic Breathing.png'</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D18" s="1"/>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="3"/>
+        <v>2612</v>
+      </c>
+      <c r="P18" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>2612</v>
+      </c>
+      <c r="R18" t="s">
+        <v>57</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/seated scapular retraction.png</v>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2612 THEN '/static/exercises/brain/seated scapular retraction.png'</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D19" s="1"/>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>2613</v>
+      </c>
+      <c r="P19" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>2613</v>
+      </c>
+      <c r="R19" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/table top arm slide.png</v>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2613 THEN '/static/exercises/brain/table top arm slide.png'</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D20" s="1"/>
+      <c r="G20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" t="s">
+        <v>47</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>2614</v>
+      </c>
+      <c r="P20" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="0"/>
+        <v>2614</v>
+      </c>
+      <c r="R20" t="s">
+        <v>57</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/supine arm slides.png</v>
+      </c>
+      <c r="Y20" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2614 THEN '/static/exercises/brain/supine arm slides.png'</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D21" s="1"/>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="3"/>
+        <v>2615</v>
+      </c>
+      <c r="P21" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="0"/>
+        <v>2615</v>
+      </c>
+      <c r="R21" t="s">
+        <v>57</v>
+      </c>
+      <c r="S21" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/heel slide.png</v>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2615 THEN '/static/exercises/brain/heel slide.png'</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D22" s="1"/>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="3"/>
+        <v>2616</v>
+      </c>
+      <c r="P22" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="0"/>
+        <v>2616</v>
+      </c>
+      <c r="R22" t="s">
+        <v>57</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/seated weight shift lateral.png</v>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2616 THEN '/static/exercises/brain/seated weight shift lateral.png'</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D23" s="1"/>
+      <c r="G23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="3"/>
+        <v>2617</v>
+      </c>
+      <c r="P23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="0"/>
+        <v>2617</v>
+      </c>
+      <c r="R23" t="s">
+        <v>57</v>
+      </c>
+      <c r="S23" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/seated weight shift antpost.png</v>
+      </c>
+      <c r="Y23" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2617 THEN '/static/exercises/brain/seated weight shift antpost.png'</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D24" s="1"/>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="3"/>
+        <v>2618</v>
+      </c>
+      <c r="P24" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="0"/>
+        <v>2618</v>
+      </c>
+      <c r="R24" t="s">
+        <v>57</v>
+      </c>
+      <c r="S24" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/seated trunk rotation.png</v>
+      </c>
+      <c r="Y24" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2618 THEN '/static/exercises/brain/seated trunk rotation.png'</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D25" s="1"/>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>2619</v>
+      </c>
+      <c r="P25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="0"/>
+        <v>2619</v>
+      </c>
+      <c r="R25" t="s">
+        <v>57</v>
+      </c>
+      <c r="S25" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/seated pelvic tilt.png</v>
+      </c>
+      <c r="Y25" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2619 THEN '/static/exercises/brain/seated pelvic tilt.png'</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D26" s="1"/>
+      <c r="G26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="3"/>
+        <v>2620</v>
+      </c>
+      <c r="P26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="0"/>
+        <v>2620</v>
+      </c>
+      <c r="R26" t="s">
+        <v>57</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/quad isometric.png</v>
+      </c>
+      <c r="Y26" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2620 THEN '/static/exercises/brain/quad isometric.png'</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D27" s="1"/>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="3"/>
+        <v>2621</v>
+      </c>
+      <c r="P27" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="0"/>
+        <v>2621</v>
+      </c>
+      <c r="R27" t="s">
+        <v>57</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/supine pelvic tilt.png</v>
+      </c>
+      <c r="Y27" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2621 THEN '/static/exercises/brain/supine pelvic tilt.png'</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.35">
+      <c r="D28" s="1"/>
+      <c r="G28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="3"/>
+        <v>2622</v>
+      </c>
+      <c r="P28" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="0"/>
+        <v>2622</v>
+      </c>
+      <c r="R28" t="s">
+        <v>57</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="1"/>
+        <v>/static/exercises/brain/towel squeeze.png</v>
+      </c>
+      <c r="Y28" t="str">
+        <f t="shared" si="2"/>
+        <v>WHEN 2622 THEN '/static/exercises/brain/towel squeeze.png'</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>